--- a/outputs/4. Moorgate Crossrail Register (Final).xlsx
+++ b/outputs/4. Moorgate Crossrail Register (Final).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,71 +489,26 @@
           <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Schema Alignment Log</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID (Reasoning)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description (Reasoning)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage (Reasoning)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category (Reasoning)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner (Reasoning)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (Reasoning)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (Reasoning)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action (Reasoning)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Opening of the Moorgate Crossrail station is delayed further.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -563,11 +518,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Regular engagement with Crossrail from now to 2020/2021. This should allow for alternative arrangements to be made should there be a delay in the delivery of Crossrail.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -578,95 +533,50 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>The Riney highways contract is due to expire in the summer of 2022. Any slippage in starting the construction programme may mean we have to consider a new Principal Contractor for the later stages of delivery.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Discussions to take place internally should this risk look more probable on how work would be transferred to a new contractor- or not</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -677,81 +587,36 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Delays to the four developments surrounding the Moorgate Crossrail station delay the final delivery phases of the MCSL project.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -761,11 +626,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Regular engagement with developers from now until the completion of the developments. This should allow for alternative arrangements to be made should there be a delay in the delivery of the developments and mean that we find out as early as possible about any delays.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -776,98 +641,53 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Infrastructure and utilities difficulties at the Moorgate junction with London Wall and with Ropermaker Street, make it difficult/too expensive to design and transform the space, as well as enhance safety.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Infrastructure Manager</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Set expectations at the earliest stage possible where it is discovered that there are major physical constraints. Work closely with internal and external stakeholders to identify design solutions to bring the work forward that might not require such extensive physical changes.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -875,95 +695,50 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Key stakeholder(s) do not endorse design options</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Ensure that Stakeholder Working Group is suitably engaged and that design options are presented with clear rationale and benefits to secure endorsement.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -974,81 +749,36 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Delays or changes to dependency projects, such as Beech Street and St. Paul's Gyratory, could impact the Moorgate Crossrail project schedule and deliverables.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1058,11 +788,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Work with internal stakeholders to monitor dependency project progress and develop contingency plans to minimize any impacts should changes or delays arise.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -1073,81 +803,36 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Breakdown in engagement with key stakeholders, such as Islington Council.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1157,11 +842,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Ensure coherent communications with stakeholders and ensure stakeholders are communicated with at strategic points throughout the project. Particularly proposed boundary solutions.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -1172,81 +857,36 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>TfL restructure may mean that no dedicated scheme sponsor / resource can be allocated to progress any required TfL approvals.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1256,96 +896,51 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Officers will seek to establish resources as early as possible and keep close contact to understand the extent of the restructure, seeking reassurance of resource if needed.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>There is a potential that the proposed scheme could impact negatively on the protected characteristics under the Equalities Act, 2010.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1355,7 +950,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Meetings with representative groups will be conducted regularly to design out issues of concern. The EA Team will be engaged regularly for design feedback. An EA plan will be prepared as part of the project.</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1370,95 +965,50 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Requirement to maintain traffic resilience/flexibility through the area restricts the development options that can be implemented.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Seek to ensure that an appropriate level of resilience is allowed for when designing Moorgate junctions at London Wall and Ropemaker Street.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -1469,59 +1019,14 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>Med</t>
         </is>
       </c>
     </row>
